--- a/backend/cosas/archivos/Modelado de Base de datos produccion lisa.xlsx
+++ b/backend/cosas/archivos/Modelado de Base de datos produccion lisa.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\Documents\projects\zona-decoracion-venvidrio\backend\cosas\archivos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\proyectos\zona-decoracion\backend\cosas\archivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E77EFF8-E33A-4B08-A02A-18F21239AFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+  <si>
+    <t>A00001</t>
+  </si>
+  <si>
+    <t>A00002</t>
+  </si>
+  <si>
+    <t>A00003</t>
+  </si>
+  <si>
+    <t>A00004</t>
+  </si>
+  <si>
+    <t>A00005</t>
+  </si>
   <si>
     <t>valmy</t>
   </si>
@@ -51,10 +65,16 @@
     <t>produccion_lisa_registro</t>
   </si>
   <si>
+    <t>fecha_registro</t>
+  </si>
+  <si>
     <t>modelo</t>
   </si>
   <si>
-    <t>id</t>
+    <t>cantidad_sacada</t>
+  </si>
+  <si>
+    <t>fecha_salida</t>
   </si>
   <si>
     <t>id_salida</t>
@@ -63,6 +83,9 @@
     <t>cantidad</t>
   </si>
   <si>
+    <t>A00006</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -72,29 +95,68 @@
     <t>produccion_lisa_inventario</t>
   </si>
   <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>modelado para la base de datos</t>
+  </si>
+  <si>
+    <t>id_inventariopl</t>
+  </si>
+  <si>
+    <t>se puede crear un nuevo modelo</t>
+  </si>
+  <si>
+    <t>solo ve los modelos existentes</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>nuevo+</t>
+  </si>
+  <si>
+    <t>solo para registro</t>
+  </si>
+  <si>
+    <t>posible select para registros y salidas</t>
+  </si>
+  <si>
+    <t>formulario_R</t>
+  </si>
+  <si>
+    <t>formulario_S</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>se vera el select de los modelos y al lado la cantidad</t>
+  </si>
+  <si>
+    <t>mensaje de error en caso de que saque mas de la cuenta</t>
+  </si>
+  <si>
+    <t>Se pueden desactivar modelos</t>
+  </si>
+  <si>
+    <t>no se ven modelos desactivados</t>
+  </si>
+  <si>
+    <t>solo se ven los activos</t>
+  </si>
+  <si>
+    <t>campo de nuevo modeo</t>
+  </si>
+  <si>
+    <t>se ven los modelos actuales mediante un select</t>
+  </si>
+  <si>
+    <t>se siguen viendo modelos vacios</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +179,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="9"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -128,12 +196,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,8 +232,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -201,20 +293,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -232,6 +315,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -241,7 +327,7 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -254,11 +340,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -268,19 +353,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,325 +658,440 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1"/>
+    <col min="8" max="8" width="17.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B1" s="25" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="10">
+        <v>46174</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="22">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="14"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="15">
+        <v>46174</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="22">
+        <v>2000</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15">
+        <v>46175</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="16">
+        <v>500</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="C11" s="15">
+        <v>46176</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="16">
+        <v>100</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="15">
+        <v>46176</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="16">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="16">
+        <v>1</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="12">
+        <f>E8+E9+E13-E24</f>
+        <v>7100</v>
+      </c>
+      <c r="K12" s="29"/>
+    </row>
+    <row r="13" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="14"/>
+      <c r="B13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="15">
+        <v>46236</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>5000</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="17">
+        <v>2</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="17">
+        <f>E10+E11+E12</f>
+        <v>6600</v>
+      </c>
+      <c r="K13" s="29"/>
+    </row>
+    <row r="14" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="8"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="29"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="29"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+      <c r="B19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G19" s="14"/>
+      <c r="H19" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="16">
+        <v>1</v>
+      </c>
+      <c r="C20" s="15">
+        <v>46208</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="16">
+        <v>500</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20" s="28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="16">
+        <v>2</v>
+      </c>
+      <c r="C21" s="15">
+        <v>46208</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="16">
+        <v>300</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="8"/>
+      <c r="B22" s="16">
+        <v>3</v>
+      </c>
+      <c r="C22" s="15">
+        <v>46208</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="16">
+        <v>500</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8"/>
+      <c r="B23" s="16">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="9">
-        <v>46174</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="22">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="14">
-        <v>46174</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="22">
-        <v>2000</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="14">
-        <v>46175</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15">
-        <v>500</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="5" t="s">
+      <c r="C23" s="15">
+        <v>46208</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="27" t="s">
+      <c r="E23" s="16">
+        <v>200</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="14">
-        <v>46176</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="15">
-        <v>100</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="15">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="J7" s="11">
-        <f>E4+E5+E9-E22</f>
-        <v>7100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="14">
-        <v>46176</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="15">
-        <v>6000</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="16">
-        <v>2</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="16">
-        <f>E6+E7+E8</f>
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="C24" s="10">
         <v>46236</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>5000</v>
-      </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="15">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14">
-        <v>46208</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E18" s="15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="15">
-        <v>2</v>
-      </c>
-      <c r="C19" s="14">
-        <v>46208</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" s="15">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="15">
-        <v>3</v>
-      </c>
-      <c r="C20" s="14">
-        <v>46208</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="15">
-        <v>4</v>
-      </c>
-      <c r="C21" s="14">
-        <v>46208</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="9">
-        <v>46236</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E22" s="10">
+      <c r="D24" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="11">
         <v>900</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="14"/>
+      <c r="F26" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="36"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="F27" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="36"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="B6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
